--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562269317</v>
+        <v>46157.93071349878</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93071349878</v>
+        <v>46157.93154424377</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93154424377</v>
+        <v>46157.93393991513</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393991513</v>
+        <v>46157.93708948795</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93708948795</v>
+        <v>46158.28210923335</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210923335</v>
+        <v>46158.29666095537</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29666095537</v>
+        <v>46158.2980576244</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980576244</v>
+        <v>46158.33381682565</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381682565</v>
+        <v>46158.36848441668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36848441668</v>
+        <v>46158.37281872945</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
